--- a/H5509_alarm.xlsx
+++ b/H5509_alarm.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12960"/>
+    <workbookView windowWidth="26385" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3690" uniqueCount="2451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3693" uniqueCount="2452">
   <si>
     <t>C_EmptySidePush--Cylinder On Sensor Can not Detect On</t>
   </si>
@@ -7383,6 +7383,9 @@
   </si>
   <si>
     <t>全部回零完成</t>
+  </si>
+  <si>
+    <t>设备未归零</t>
   </si>
 </sst>
 </file>
@@ -8325,7 +8328,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1230"/>
+  <dimension ref="A1:E1231"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="3.5" style="1" customWidth="1"/>
@@ -29248,6 +29251,23 @@
         <v>2336</v>
       </c>
     </row>
+    <row r="1231" spans="1:5">
+      <c r="A1231" s="1">
+        <v>17</v>
+      </c>
+      <c r="B1231" s="1">
+        <v>1400445</v>
+      </c>
+      <c r="C1231" s="2" t="s">
+        <v>2451</v>
+      </c>
+      <c r="D1231" s="2" t="s">
+        <v>2451</v>
+      </c>
+      <c r="E1231" s="1" t="s">
+        <v>2347</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E1230" etc:filterBottomFollowUsedRange="0">
     <extLst/>
